--- a/data/all_datasets/REDD/REDD_House6_stats/2026-03-29.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-03-29.xlsx
@@ -17927,7 +17927,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>浴室插座</t>
+          <t>电吹风</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>浴室插座</t>
+          <t>电吹风</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E33" t="n">
